--- a/artfynd/A 30393-2024 artfynd.xlsx
+++ b/artfynd/A 30393-2024 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>118675788</v>
       </c>
       <c r="B6" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 30393-2024 artfynd.xlsx
+++ b/artfynd/A 30393-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112606585</v>
+        <v>118675788</v>
       </c>
       <c r="B4" t="n">
-        <v>77608</v>
+        <v>78229</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,20 +942,24 @@
           <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Polcirkeln, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768523</v>
+        <v>768539</v>
       </c>
       <c r="R4" t="n">
-        <v>7399383</v>
+        <v>7399401</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,17 +983,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,224 +1017,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>112606582</v>
-      </c>
-      <c r="B5" t="n">
-        <v>89936</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1588</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Violmussling</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Trichaptum laricinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Polcirkeln, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>768374</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7398969</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>118675788</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78229</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6446</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Polcirkeln, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>768539</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7399401</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-07-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
